--- a/Result/profitability/2751.xlsx
+++ b/Result/profitability/2751.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM26"/>
+  <dimension ref="A1:AM27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3732,6 +3732,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2751</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>507</v>
+      </c>
+      <c r="D27" t="n">
+        <v>247</v>
+      </c>
+      <c r="E27" t="n">
+        <v>260</v>
+      </c>
+      <c r="F27" t="n">
+        <v>51.35</v>
+      </c>
+      <c r="G27" t="n">
+        <v>38</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>7.46%</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>37</v>
+      </c>
+      <c r="K27" t="n">
+        <v>28</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.2075</v>
+      </c>
+      <c r="N27" t="n">
+        <v>49.12125</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.3899999999999999</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.386138613861386</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.300000000000004</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.02597402597402598</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.3699999999999999</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.3592233009708736</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0.2000000000000028</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.003910068426197455</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK27" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
